--- a/test/ifa/dat/DOCENTES IFALFA 2025_020240.xlsx
+++ b/test/ifa/dat/DOCENTES IFALFA 2025_020240.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId2"/>

--- a/test/ifa/dat/DOCENTES IFALFA 2025_020240.xlsx
+++ b/test/ifa/dat/DOCENTES IFALFA 2025_020240.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" state="visible" r:id="rId2"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="117">
   <si>
     <t xml:space="preserve">1RO INICIAL A </t>
   </si>
@@ -170,9 +170,21 @@
     <t xml:space="preserve">VIOLIN</t>
   </si>
   <si>
+    <t xml:space="preserve">HADIT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELMA, OMAR</t>
+  </si>
+  <si>
     <t xml:space="preserve">GUITARRA</t>
   </si>
   <si>
+    <t xml:space="preserve">CRISTIAN, LUIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIAN, OMAR</t>
+  </si>
+  <si>
     <t xml:space="preserve">1RO BASICO A </t>
   </si>
   <si>
@@ -354,9 +366,6 @@
   </si>
   <si>
     <t xml:space="preserve">INSTRUMENTO COMPLEMENTARIO </t>
-  </si>
-  <si>
-    <t xml:space="preserve">HADIT </t>
   </si>
   <si>
     <t xml:space="preserve">SELMA </t>
@@ -411,7 +420,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -434,6 +443,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE0C2CD"/>
         <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFAA95"/>
+        <bgColor rgb="FFFFCC99"/>
       </patternFill>
     </fill>
     <fill>
@@ -496,7 +511,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -541,15 +556,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -561,11 +580,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -621,7 +640,7 @@
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FFA9D18E"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFFFAA95"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
@@ -763,7 +782,7 @@
       <c r="G6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="11" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="7" t="s">
@@ -881,7 +900,7 @@
       </c>
     </row>
     <row r="12" customFormat="false" ht="46.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="12" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -975,7 +994,7 @@
       <c r="I15" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="11" t="s">
         <v>20</v>
       </c>
       <c r="K15" s="0" t="s">
@@ -1001,7 +1020,7 @@
       <c r="C16" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="13" t="s">
         <v>47</v>
       </c>
       <c r="E16" s="7" t="s">
@@ -1011,55 +1030,78 @@
         <v>48</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="K16" s="10"/>
+        <v>21</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="N16" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="O16" s="0" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="G17" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>21</v>
       </c>
+      <c r="K17" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="N17" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="O17" s="0" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="13" t="s">
-        <v>50</v>
+      <c r="B18" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>24</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="6" t="s">
@@ -1068,16 +1110,12 @@
       <c r="C19" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="14" t="s">
-        <v>55</v>
+      <c r="D19" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19" s="8"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
@@ -1090,12 +1128,8 @@
         <v>10</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" s="8"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
@@ -1108,32 +1142,24 @@
         <v>29</v>
       </c>
       <c r="E21" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="16"/>
+    </row>
+    <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="15"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1143,11 +1169,11 @@
       <c r="C24" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D24" s="14" t="s">
-        <v>55</v>
+      <c r="D24" s="15" t="s">
+        <v>59</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1161,7 +1187,7 @@
         <v>10</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1172,10 +1198,10 @@
         <v>25</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1186,25 +1212,25 @@
         <v>25</v>
       </c>
       <c r="D27" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="29" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="13" t="s">
-        <v>61</v>
+      <c r="B29" s="14" t="s">
+        <v>65</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1215,10 +1241,10 @@
         <v>8</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1232,7 +1258,7 @@
         <v>10</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1243,37 +1269,37 @@
         <v>8</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="7"/>
       <c r="E33" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="44.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="13" t="s">
-        <v>65</v>
+      <c r="B35" s="14" t="s">
+        <v>69</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1284,10 +1310,10 @@
         <v>8</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1301,7 +1327,7 @@
         <v>10</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1312,25 +1338,25 @@
         <v>8</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="40" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="E40" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1338,13 +1364,13 @@
         <v>4</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1352,13 +1378,13 @@
         <v>5</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1366,28 +1392,28 @@
         <v>6</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="45" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="13" t="s">
-        <v>74</v>
+      <c r="B45" s="14" t="s">
+        <v>78</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1398,10 +1424,10 @@
         <v>44</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1413,7 +1439,7 @@
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1424,25 +1450,25 @@
         <v>44</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="50" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="16" t="s">
-        <v>79</v>
+      <c r="B50" s="17" t="s">
+        <v>83</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1450,10 +1476,10 @@
         <v>4</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E51" s="7"/>
     </row>
@@ -1462,7 +1488,7 @@
         <v>5</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
@@ -1472,28 +1498,28 @@
         <v>6</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="55" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1504,7 +1530,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E56" s="7"/>
     </row>
@@ -1526,21 +1552,21 @@
         <v>8</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="6" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E59" s="7"/>
     </row>
@@ -1552,7 +1578,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>43</v>
@@ -1560,17 +1586,17 @@
     </row>
     <row r="61" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="62" customFormat="false" ht="47.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B62" s="16" t="s">
-        <v>90</v>
+      <c r="B62" s="17" t="s">
+        <v>94</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1580,8 +1606,8 @@
       <c r="C63" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D63" s="14" t="s">
-        <v>94</v>
+      <c r="D63" s="15" t="s">
+        <v>98</v>
       </c>
       <c r="E63" s="7"/>
     </row>
@@ -1605,25 +1631,25 @@
         <v>34</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="67" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B67" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="C67" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D67" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E67" s="17" t="s">
-        <v>82</v>
+      <c r="B67" s="17" t="s">
+        <v>100</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1631,13 +1657,13 @@
         <v>4</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D68" s="7" t="s">
         <v>28</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1645,13 +1671,13 @@
         <v>5</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1659,13 +1685,13 @@
         <v>6</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="24.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1754,7 +1780,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="32.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>4</v>
@@ -1766,7 +1792,7 @@
         <v>6</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1777,42 +1803,42 @@
       <c r="F3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="35.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="18" t="s">
-        <v>101</v>
+      <c r="B4" s="19" t="s">
+        <v>105</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="18" t="s">
-        <v>104</v>
+      <c r="B5" s="19" t="s">
+        <v>108</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18" t="s">
-        <v>106</v>
+      <c r="B6" s="19" t="s">
+        <v>110</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>28</v>
@@ -1828,8 +1854,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="18" t="s">
-        <v>107</v>
+      <c r="B7" s="19" t="s">
+        <v>111</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>24</v>
@@ -1845,25 +1871,25 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="18" t="s">
-        <v>108</v>
+      <c r="B8" s="19" t="s">
+        <v>112</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="18" t="s">
-        <v>109</v>
+      <c r="B9" s="19" t="s">
+        <v>113</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>8</v>
@@ -1875,29 +1901,29 @@
         <v>8</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="18" t="s">
-        <v>110</v>
+      <c r="B10" s="19" t="s">
+        <v>114</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="18" t="s">
-        <v>113</v>
+      <c r="B11" s="19" t="s">
+        <v>116</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>34</v>
